--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_24-11-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_24-11-2025.xlsx
@@ -1053,7 +1053,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>£20.51</t>
+          <t>£20.42</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
